--- a/data/dividends_info_20261018.xlsx
+++ b/data/dividends_info_20261018.xlsx
@@ -2100,7 +2100,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2117,7 +2117,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2127,14 +2127,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -2365,14 +2365,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2389,7 +2389,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2406,7 +2406,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2423,7 +2423,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2433,14 +2433,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2450,14 +2450,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2474,7 +2474,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2491,7 +2491,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2508,7 +2508,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2518,14 +2518,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2535,14 +2535,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2552,14 +2552,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2576,7 +2576,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2610,7 +2610,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2644,7 +2644,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2661,7 +2661,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2695,7 +2695,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2705,14 +2705,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2722,14 +2722,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2739,14 +2739,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>JUVENTUS F.C. S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2756,14 +2756,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2773,14 +2773,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2790,14 +2790,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>JUVENTUS F.C. S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2824,14 +2824,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2865,7 +2865,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2882,7 +2882,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2909,14 +2909,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2950,7 +2950,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2967,7 +2967,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3086,7 +3086,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3096,14 +3096,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3130,14 +3130,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3154,7 +3154,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3171,7 +3171,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3188,7 +3188,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3198,14 +3198,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3222,7 +3222,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3232,14 +3232,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3249,14 +3249,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3266,14 +3266,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3307,7 +3307,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3341,7 +3341,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3358,7 +3358,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3368,14 +3368,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3392,7 +3392,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3409,7 +3409,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3426,7 +3426,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3443,7 +3443,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3460,7 +3460,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3477,7 +3477,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3494,7 +3494,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3511,7 +3511,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3528,7 +3528,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3545,7 +3545,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3562,7 +3562,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3572,14 +3572,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3589,14 +3589,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3606,14 +3606,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3630,7 +3630,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3640,14 +3640,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3698,7 +3698,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3715,7 +3715,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3732,7 +3732,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3742,14 +3742,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3759,14 +3759,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3776,14 +3776,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3793,14 +3793,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3817,7 +3817,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3827,14 +3827,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3844,14 +3844,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3868,7 +3868,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3878,14 +3878,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3902,7 +3902,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3919,7 +3919,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3936,7 +3936,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3953,7 +3953,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3963,14 +3963,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3980,14 +3980,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4014,14 +4014,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4048,14 +4048,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4072,7 +4072,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4089,7 +4089,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4106,7 +4106,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4123,7 +4123,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4140,7 +4140,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4174,7 +4174,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4184,14 +4184,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4208,7 +4208,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4225,7 +4225,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4242,7 +4242,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4252,14 +4252,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4276,7 +4276,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4293,7 +4293,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4310,7 +4310,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4327,7 +4327,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4337,14 +4337,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4354,14 +4354,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4378,7 +4378,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4395,7 +4395,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4405,14 +4405,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4429,7 +4429,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4439,14 +4439,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4463,7 +4463,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4480,7 +4480,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4507,14 +4507,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4531,7 +4531,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4548,7 +4548,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4565,7 +4565,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4575,14 +4575,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4599,7 +4599,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4609,14 +4609,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4633,7 +4633,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4650,7 +4650,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4667,7 +4667,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4684,7 +4684,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4694,14 +4694,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4718,7 +4718,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4762,14 +4762,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4786,7 +4786,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4803,7 +4803,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4820,7 +4820,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4830,14 +4830,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4854,7 +4854,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4871,7 +4871,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4888,7 +4888,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4905,7 +4905,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4915,14 +4915,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4939,7 +4939,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4949,14 +4949,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4973,7 +4973,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4990,7 +4990,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5007,7 +5007,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5017,14 +5017,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5041,7 +5041,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5058,7 +5058,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5068,14 +5068,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5092,7 +5092,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5119,14 +5119,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5143,7 +5143,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5153,14 +5153,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5177,7 +5177,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5187,14 +5187,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5211,7 +5211,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5221,14 +5221,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5245,7 +5245,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5262,7 +5262,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5279,7 +5279,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5289,14 +5289,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5313,7 +5313,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5323,14 +5323,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5347,7 +5347,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5364,7 +5364,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5381,7 +5381,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5398,7 +5398,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5415,7 +5415,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5432,7 +5432,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5449,7 +5449,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5466,7 +5466,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5483,7 +5483,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5500,7 +5500,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5517,7 +5517,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5527,14 +5527,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5551,7 +5551,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5561,14 +5561,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5585,7 +5585,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5602,7 +5602,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5612,14 +5612,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5629,14 +5629,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5653,7 +5653,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5670,7 +5670,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5704,7 +5704,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -5721,7 +5721,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -5738,7 +5738,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -5755,7 +5755,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -5772,7 +5772,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5789,7 +5789,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5806,7 +5806,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5816,14 +5816,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5833,14 +5833,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5857,7 +5857,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -5874,7 +5874,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -5891,7 +5891,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -5925,7 +5925,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -5942,7 +5942,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -5997,44 +5997,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CIRCLE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-11-17</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>